--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="319">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:23:16+00:00</t>
+    <t>2026-08-10T12:51:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>病理で取得または使用される画像に関わる情報を記録するためのプロファイル</t>
+    <t>病理で取得または使用される画像に関わる情報を扱うプロファイル</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -271,7 +271,7 @@
 </t>
   </si>
   <si>
-    <t>病理で取得または使用される画像に関わる情報</t>
+    <t>病理で取得または使用される画像に関わる情報。</t>
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
@@ -506,10 +506,10 @@
 </t>
   </si>
   <si>
-    <t>他のシステムから依頼されたオーダ情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>他のシステムから依頼されたオーダ情報</t>
+    <t>他のシステムから依頼されたオーダ情報。【詳細参照】</t>
+  </si>
+  <si>
+    <t>他のシステムから依頼されたオーダ情報。</t>
   </si>
   <si>
     <t>通常、依頼元となるServiceRequestリソースを参照する。他のシステムと連携していない場合は参照不要。</t>
@@ -535,13 +535,13 @@
 </t>
   </si>
   <si>
-    <t>参照されるイベントの一部【詳細参照】</t>
-  </si>
-  <si>
-    <t>参照されるイベントの一部</t>
-  </si>
-  <si>
-    <t>使用する場合は、基底にあるDefinition、Requirement、Commentsの内容を参考に使用する。</t>
+    <t>参照されるイベントの一部。【詳細参照】</t>
+  </si>
+  <si>
+    <t>参照されるイベントの一部。</t>
+  </si>
+  <si>
+    <t>使用する場合は、基底にある Definition、Requirement、Comments の内容を参考に使用する。</t>
   </si>
   <si>
     <t>E.g. Drug administration as part of a procedure, procedure as part of observation, etc.</t>
@@ -556,16 +556,13 @@
     <t>Media.status</t>
   </si>
   <si>
-    <t>メディアのステータス【詳細参照】</t>
-  </si>
-  <si>
-    <t>メディアのステータス</t>
-  </si>
-  <si>
-    <t>"completed"を指定する。</t>
-  </si>
-  <si>
-    <t>completed</t>
+    <t>メディアのステータス。【詳細参照】</t>
+  </si>
+  <si>
+    <t>メディアのステータス。</t>
+  </si>
+  <si>
+    <t>"completed" を指定する。</t>
   </si>
   <si>
     <t>required</t>
@@ -596,10 +593,10 @@
 </t>
   </si>
   <si>
-    <t>メディアの種類【詳細参照】</t>
-  </si>
-  <si>
-    <t>メディアの種類</t>
+    <t>メディアの種類。【詳細参照】</t>
+  </si>
+  <si>
+    <t>メディアの種類。</t>
   </si>
   <si>
     <t>使用する場合は、"image"を使用する。</t>
@@ -626,10 +623,10 @@
     <t>Media.modality</t>
   </si>
   <si>
-    <t>メディアを取得・撮影した装置（モダリティ）【詳細参照】</t>
-  </si>
-  <si>
-    <t>メディアを取得・撮影した装置（モダリティ）</t>
+    <t>メディアを取得・撮影した装置（モダリティ）。【詳細参照】</t>
+  </si>
+  <si>
+    <t>メディアを取得・撮影した装置（モダリティ）。</t>
   </si>
   <si>
     <t>使用する場合、臓器画像は"XC"、顕微鏡画像は"GM"を指定する。</t>
@@ -659,10 +656,10 @@
     <t>Media.view</t>
   </si>
   <si>
-    <t>メディアのイメージングビュー【詳細参照】</t>
-  </si>
-  <si>
-    <t>メディアのイメージングビュー</t>
+    <t>メディアのイメージングビュー。【詳細参照】</t>
+  </si>
+  <si>
+    <t>メディアのイメージングビュー。</t>
   </si>
   <si>
     <t>病理では原則使用しない。将来的にニーズが出てきた場合には検討する。</t>
@@ -684,10 +681,10 @@
 </t>
   </si>
   <si>
-    <t>メディアの対象患者に関する情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>メディアの対象患者に関する情報</t>
+    <t>メディアの対象患者に関する情報。【詳細参照】</t>
+  </si>
+  <si>
+    <t>メディアの対象患者に関する情報。</t>
   </si>
   <si>
     <t>JP Core Patientリソースを参照する。</t>
@@ -716,10 +713,10 @@
 </t>
   </si>
   <si>
-    <t>このメディアが生成されるきっかけとなった情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>このメディアが生成されるきっかけとなった情報</t>
+    <t>このメディアが生成されるきっかけとなった情報。【詳細参照】</t>
+  </si>
+  <si>
+    <t>このメディアが生成されるきっかけとなった情報。</t>
   </si>
   <si>
     <t>病理では原則使用しない。</t>
@@ -748,10 +745,10 @@
 Period</t>
   </si>
   <si>
-    <t>このメディアが生成された日時【詳細参照】</t>
-  </si>
-  <si>
-    <t>このメディアが生成された日時</t>
+    <t>このメディアが生成された日時。【詳細参照】</t>
+  </si>
+  <si>
+    <t>このメディアが生成された日時。</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -770,7 +767,7 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReportのStatusがFinalになった日時（レポート確定日時）</t>
+    <t>DiagnosticReportのStatusがFinalになった日時（レポート確定日時）。</t>
   </si>
   <si>
     <t>[`Meta.lastUpdated`](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) の時間と同じかもしれません。特定の更新のために審査と確認が必要な観察については、新しいバージョンを再度審査および確認する必要がない非臨床的に重要でない更新により、リソース自体の `lastUpdated` 時間と同じでない場合があります。</t>
@@ -792,10 +789,10 @@
 </t>
   </si>
   <si>
-    <t>画像を取得した人【詳細参照】</t>
-  </si>
-  <si>
-    <t>画像を取得した人</t>
+    <t>画像を取得した人。【詳細参照】</t>
+  </si>
+  <si>
+    <t>画像を取得した人。</t>
   </si>
   <si>
     <t>病理では未使用。</t>
@@ -816,10 +813,10 @@
     <t>Media.reasonCode</t>
   </si>
   <si>
-    <t>このメディアが生成された理由【詳細参照】</t>
-  </si>
-  <si>
-    <t>このメディアが生成された理由</t>
+    <t>このメディアが生成された理由。【詳細参照】</t>
+  </si>
+  <si>
+    <t>このメディアが生成された理由。</t>
   </si>
   <si>
     <t>病理では省略してよい。</t>
@@ -843,10 +840,10 @@
     <t>Media.bodySite</t>
   </si>
   <si>
-    <t>このメディアの対象となる解剖学的部位【詳細参照】</t>
-  </si>
-  <si>
-    <t>このメディアの対象となる解剖学的部位</t>
+    <t>このメディアの対象となる解剖学的部位。【詳細参照】</t>
+  </si>
+  <si>
+    <t>このメディアの対象となる解剖学的部位。</t>
   </si>
   <si>
     <t>病理では省略してよい。写真毎に部位が設定されている場合は指定する。</t>
@@ -874,10 +871,10 @@
 </t>
   </si>
   <si>
-    <t>このメディアを生成した装置名【詳細参照】</t>
-  </si>
-  <si>
-    <t>このメディアを生成した装置名</t>
+    <t>このメディアを生成した装置名。【詳細参照】</t>
+  </si>
+  <si>
+    <t>このメディアを生成した装置名。</t>
   </si>
   <si>
     <t>.participation[typeCode="DEV"].role.player.Entity[classCode="DEV"].name</t>
@@ -893,10 +890,10 @@
 </t>
   </si>
   <si>
-    <t>メディアの収集に使用されるデバイス【詳細参照】</t>
-  </si>
-  <si>
-    <t>メディアの収集に使用されるデバイス</t>
+    <t>メディアの収集に使用されるデバイス。【詳細参照】</t>
+  </si>
+  <si>
+    <t>メディアの収集に使用されるデバイス。</t>
   </si>
   <si>
     <t>participation[typeCode=DEV]</t>
@@ -915,10 +912,10 @@
 </t>
   </si>
   <si>
-    <t>画像の高さ（ピクセル単位）（写真/ビデオ）【詳細参照】</t>
-  </si>
-  <si>
-    <t>画像の高さ（ピクセル単位）（写真/ビデオ）</t>
+    <t>画像の高さ（ピクセル単位）（写真/ビデオ）。【詳細参照】</t>
+  </si>
+  <si>
+    <t>画像の高さ（ピクセル単位）（写真/ビデオ）。</t>
   </si>
   <si>
     <t>使用する場合は、画像の高さ（ピクセル単位）（写真）を指定する。</t>
@@ -933,10 +930,10 @@
     <t>Media.width</t>
   </si>
   <si>
-    <t>画像の幅（ピクセル単位）（写真/ビデオ）【詳細参照】</t>
-  </si>
-  <si>
-    <t>画像の幅（ピクセル単位）（写真/ビデオ）</t>
+    <t>画像の幅（ピクセル単位）（写真/ビデオ）。【詳細参照】</t>
+  </si>
+  <si>
+    <t>画像の幅（ピクセル単位）（写真/ビデオ）。</t>
   </si>
   <si>
     <t>使用する場合は、画像の幅（ピクセル単位）（写真）を指定する。</t>
@@ -948,10 +945,10 @@
     <t>Media.frames</t>
   </si>
   <si>
-    <t>フレーム数【詳細参照】</t>
-  </si>
-  <si>
-    <t>フレーム数</t>
+    <t>フレーム数。【詳細参照】</t>
+  </si>
+  <si>
+    <t>フレーム数。</t>
   </si>
   <si>
     <t>Media.duration</t>
@@ -961,10 +958,10 @@
 </t>
   </si>
   <si>
-    <t>ビデオ映像・音声向けの、秒単位の録画・記録時間【詳細参照】</t>
-  </si>
-  <si>
-    <t>ビデオ映像・音声向けの、秒単位の録画・記録時間</t>
+    <t>ビデオ映像・音声向けの、秒単位の録画・記録時間。【詳細参照】</t>
+  </si>
+  <si>
+    <t>ビデオ映像・音声向けの、秒単位の録画・記録時間。</t>
   </si>
   <si>
     <t>~0028,0002</t>
@@ -977,7 +974,7 @@
 </t>
   </si>
   <si>
-    <t>埋め込まれたメディアの実際のコンテンツ、またはメディアソースファイルへの直接参照</t>
+    <t>埋め込まれたメディアの実際のコンテンツ、またはメディアソースファイルへの直接参照。</t>
   </si>
   <si>
     <t>推奨コンテンツタイプ：image/jpeg、image/png、image/tiff、video/mpeg、audio/mp4、application/dicom。application/dicomには転送構文をパラメータとして含めることができます。時間をカバーするメディア（動画/音声）の場合、content.creationTimeは終了時間です。作成時間は追跡、バージョンの整理および検索に使用されます。</t>
@@ -993,7 +990,7 @@
 </t>
   </si>
   <si>
-    <t>メディアについてのコメント</t>
+    <t>メディアについてのコメント。</t>
   </si>
   <si>
     <t>観察、結論などに使用しないでください。代わりに、Media/ImagingStudyリソースに基づく[観察]を使用してください。</t>
@@ -3013,28 +3010,28 @@
         <v>81</v>
       </c>
       <c r="S14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="T14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X14" t="s" s="2">
+      <c r="Y14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -3067,19 +3064,19 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>81</v>
@@ -3090,10 +3087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3116,19 +3113,19 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3153,14 +3150,14 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>193</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
       </c>
@@ -3177,7 +3174,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -3195,10 +3192,10 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3215,10 +3212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3241,16 +3238,16 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3276,14 +3273,14 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
       </c>
@@ -3300,7 +3297,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -3315,16 +3312,16 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
@@ -3338,10 +3335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3364,16 +3361,16 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3399,14 +3396,14 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
       </c>
@@ -3423,7 +3420,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -3441,7 +3438,7 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>81</v>
@@ -3461,10 +3458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3487,16 +3484,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3546,7 +3543,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -3561,16 +3558,16 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -3584,14 +3581,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3610,19 +3607,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -3671,7 +3668,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -3686,13 +3683,13 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -3709,14 +3706,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3735,16 +3732,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>237</v>
-      </c>
       <c r="N20" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3794,7 +3791,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -3809,13 +3806,13 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -3832,10 +3829,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3858,16 +3855,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3917,7 +3914,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -3935,16 +3932,16 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -3955,10 +3952,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3981,16 +3978,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4040,7 +4037,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4055,16 +4052,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -4078,10 +4075,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4104,16 +4101,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4139,14 +4136,14 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="Z23" t="s" s="2">
-        <v>262</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4163,7 +4160,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4178,13 +4175,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4201,10 +4198,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4227,16 +4224,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4262,14 +4259,14 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>271</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4286,7 +4283,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4304,30 +4301,30 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AM24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4350,16 +4347,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="N25" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4409,7 +4406,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -4427,13 +4424,13 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -4447,10 +4444,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4473,16 +4470,16 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="N26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4532,7 +4529,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -4550,30 +4547,30 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4596,16 +4593,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4655,7 +4652,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -4673,13 +4670,13 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -4693,10 +4690,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4719,16 +4716,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4778,7 +4775,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -4796,13 +4793,13 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -4816,10 +4813,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4842,16 +4839,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="N29" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4901,7 +4898,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -4919,7 +4916,7 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
@@ -4939,10 +4936,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4965,16 +4962,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>306</v>
-      </c>
       <c r="N30" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5024,7 +5021,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5042,13 +5039,13 @@
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5062,10 +5059,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5088,16 +5085,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5147,7 +5144,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>90</v>
@@ -5165,7 +5162,7 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
@@ -5185,10 +5182,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5211,16 +5208,16 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5270,7 +5267,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5285,19 +5282,19 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:51:50+00:00</t>
+    <t>2026-08-12T07:04:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>病理で取得または使用される画像に関わる情報を扱うプロファイル</t>
+    <t>このプロファイルはMediaリソースに対して、病理で取得または使用される画像に関わるデータを送受信するための制約と拡張を定めたものである。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -502,7 +502,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1|CarePlan|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|CarePlan)
 </t>
   </si>
   <si>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:04:31+00:00</t>
+    <t>2026-08-12T07:45:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="392">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:45:23+00:00</t>
+    <t>2026-08-12T12:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -620,6 +620,234 @@
     <t>FiveWs.class</t>
   </si>
   <si>
+    <t>Media.type.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Media.type.extension</t>
+  </si>
+  <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Media.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Media.type.coding.id</t>
+  </si>
+  <si>
+    <t>Media.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Media.type.coding.system</t>
+  </si>
+  <si>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Media.type.coding.version</t>
+  </si>
+  <si>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Media.type.coding.code</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Media.type.coding.display</t>
+  </si>
+  <si>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Media.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Media.type.text</t>
+  </si>
+  <si>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Media.modality</t>
   </si>
   <si>
@@ -865,10 +1093,6 @@
   </si>
   <si>
     <t>Media.deviceName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>このメディアを生成した装置名。【詳細参照】</t>
@@ -1306,11 +1530,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ32"/>
+  <dimension ref="A1:AQ43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="20.36328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="20.36328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="26.12109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="26.12109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1337,7 +1561,7 @@
     <col min="26" max="26" width="40.98046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.0546875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3235,20 +3459,18 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N16" t="s" s="2">
         <v>198</v>
       </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -3273,31 +3495,31 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -3309,19 +3531,19 @@
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
@@ -3335,21 +3557,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -3358,19 +3580,19 @@
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3396,49 +3618,49 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>81</v>
@@ -3458,10 +3680,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3472,7 +3694,7 @@
         <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>81</v>
@@ -3484,18 +3706,20 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
@@ -3543,34 +3767,34 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -3581,14 +3805,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3604,23 +3828,19 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
       </c>
@@ -3668,7 +3888,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -3680,16 +3900,16 @@
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -3706,21 +3926,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>233</v>
+        <v>135</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -3729,19 +3949,19 @@
         <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>234</v>
+        <v>136</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3779,40 +3999,40 @@
         <v>81</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>237</v>
+        <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>239</v>
+        <v>81</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -3829,10 +4049,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3855,18 +4075,20 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
       </c>
@@ -3914,7 +4136,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -3926,22 +4148,22 @@
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -3952,10 +4174,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3978,16 +4200,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>248</v>
+        <v>196</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4037,7 +4259,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4049,22 +4271,22 @@
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>252</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>254</v>
+        <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>255</v>
+        <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>81</v>
+        <v>236</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>81</v>
@@ -4075,10 +4297,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4089,7 +4311,7 @@
         <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4101,24 +4323,24 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>81</v>
@@ -4136,13 +4358,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>260</v>
+        <v>81</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>261</v>
+        <v>81</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -4160,34 +4382,34 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -4198,10 +4420,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4224,18 +4446,18 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4259,13 +4481,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4283,7 +4505,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4295,13 +4517,13 @@
         <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>81</v>
@@ -4310,21 +4532,21 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>272</v>
+        <v>81</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>273</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4347,18 +4569,20 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
       </c>
@@ -4406,7 +4630,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -4418,22 +4642,22 @@
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>279</v>
+        <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>81</v>
+        <v>260</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -4444,10 +4668,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4470,18 +4694,20 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>281</v>
+        <v>196</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
       </c>
@@ -4529,7 +4755,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -4541,13 +4767,13 @@
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -4556,21 +4782,21 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>286</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4593,16 +4819,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4628,13 +4854,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -4652,7 +4878,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -4667,16 +4893,16 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>81</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -4690,10 +4916,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4716,16 +4942,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4751,13 +4977,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>81</v>
+        <v>285</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -4775,7 +5001,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -4793,13 +5019,13 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -4813,10 +5039,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4842,13 +5068,13 @@
         <v>288</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4898,7 +5124,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -4913,16 +5139,16 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -4936,14 +5162,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>81</v>
+        <v>297</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4962,18 +5188,20 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5021,7 +5249,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5036,16 +5264,16 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>81</v>
+        <v>303</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5059,18 +5287,18 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>81</v>
+        <v>307</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>90</v>
@@ -5091,10 +5319,10 @@
         <v>309</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5144,10 +5372,10 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>90</v>
@@ -5159,13 +5387,13 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5182,10 +5410,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5196,7 +5424,7 @@
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -5205,19 +5433,19 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5267,13 +5495,13 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
@@ -5282,24 +5510,1377 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>81</v>
+        <v>319</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ32" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T12:14:47+00:00</t>
+    <t>2026-08-12T12:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T12:53:42+00:00</t>
+    <t>2026-08-12T13:21:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:21:20+00:00</t>
+    <t>2026-08-13T00:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T00:17:30+00:00</t>
+    <t>2026-08-13T00:49:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T00:49:15+00:00</t>
+    <t>2026-08-13T01:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T01:04:13+00:00</t>
+    <t>2026-08-13T01:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="391">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T01:37:50+00:00</t>
+    <t>2026-08-13T08:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -860,37 +860,34 @@
     <t>使用する場合、臓器画像は"XC"、顕微鏡画像は"GM"を指定する。</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>0008,0060 | 0008,1032</t>
+  </si>
+  <si>
+    <t>Media.view</t>
+  </si>
+  <si>
+    <t>メディアのイメージングビュー。【詳細参照】</t>
+  </si>
+  <si>
+    <t>メディアのイメージングビュー。</t>
+  </si>
+  <si>
+    <t>病理では原則使用しない。将来的にニーズが出てきた場合には検討する。</t>
+  </si>
+  <si>
     <t>example</t>
-  </si>
-  <si>
-    <t>画像の種類に関する詳細情報-種類、目的、または生成に使用される機器の種類についての情報。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/media-modality|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>0008,0060 | 0008,1032</t>
-  </si>
-  <si>
-    <t>Media.view</t>
-  </si>
-  <si>
-    <t>メディアのイメージングビュー。【詳細参照】</t>
-  </si>
-  <si>
-    <t>メディアのイメージングビュー。</t>
-  </si>
-  <si>
-    <t>病理では原則使用しない。将来的にニーズが出てきた場合には検討する。</t>
   </si>
   <si>
     <t>画像を収集する際に使用される投影イメージングビュー。</t>
@@ -1557,8 +1554,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="42.01953125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="40.98046875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.0390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4854,13 +4851,11 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y27" s="2"/>
+      <c r="Z27" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -4893,16 +4888,16 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -4916,10 +4911,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4945,13 +4940,13 @@
         <v>185</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4977,14 +4972,14 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5001,7 +4996,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5019,7 +5014,7 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
@@ -5039,10 +5034,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5065,16 +5060,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5124,7 +5119,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5139,16 +5134,16 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5162,14 +5157,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5188,19 +5183,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5249,7 +5244,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5264,13 +5259,13 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5287,14 +5282,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5313,16 +5308,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M31" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="N31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5372,7 +5367,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5387,13 +5382,13 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5410,10 +5405,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5436,16 +5431,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5495,7 +5490,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5513,16 +5508,16 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -5533,10 +5528,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5559,16 +5554,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5618,7 +5613,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -5633,16 +5628,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -5656,10 +5651,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5685,13 +5680,13 @@
         <v>185</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5717,14 +5712,14 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
       </c>
@@ -5741,7 +5736,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -5756,13 +5751,13 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5779,10 +5774,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5808,13 +5803,13 @@
         <v>185</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5840,14 +5835,14 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>344</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
       </c>
@@ -5864,7 +5859,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -5882,30 +5877,30 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP35" t="s" s="2">
+      <c r="AQ35" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>347</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5931,13 +5926,13 @@
         <v>196</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>350</v>
-      </c>
       <c r="N36" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5987,7 +5982,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6005,13 +6000,13 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6025,10 +6020,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6051,16 +6046,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>356</v>
-      </c>
       <c r="N37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6110,7 +6105,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6128,30 +6123,30 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6174,16 +6169,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6233,7 +6228,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6251,13 +6246,13 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6271,10 +6266,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6297,16 +6292,16 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6356,7 +6351,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6374,13 +6369,13 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6394,10 +6389,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6420,16 +6415,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>374</v>
-      </c>
       <c r="N40" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6479,7 +6474,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6497,7 +6492,7 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
@@ -6517,10 +6512,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6543,16 +6538,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="N41" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6602,7 +6597,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -6620,13 +6615,13 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6640,10 +6635,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6666,16 +6661,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6725,7 +6720,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>90</v>
@@ -6743,7 +6738,7 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
@@ -6763,10 +6758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6789,16 +6784,16 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6848,7 +6843,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -6863,19 +6858,19 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:49:13+00:00</t>
+    <t>2026-08-13T13:00:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T13:00:31+00:00</t>
+    <t>2026-08-13T13:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T13:31:56+00:00</t>
+    <t>2026-08-13T23:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:21:35+00:00</t>
+    <t>2026-08-13T23:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-media-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:54:59+00:00</t>
+    <t>2026-08-19T04:30:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
